--- a/docs/testing/artifacts/atlas-document-school-grouping-02/Dispatch-explicit-Vinh-Tan.xlsx
+++ b/docs/testing/artifacts/atlas-document-school-grouping-02/Dispatch-explicit-Vinh-Tan.xlsx
@@ -814,7 +814,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="23" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
